--- a/sources/table_normalization/xlsx/economy-table120.xlsx
+++ b/sources/table_normalization/xlsx/economy-table120.xlsx
@@ -172,13 +172,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="7">
-    <numFmt numFmtId="166" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="167" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="168" formatCode="dd/mm/yy;@"/>
-    <numFmt numFmtId="169" formatCode="[$£-809]#,##0.00;&quot;-&quot;[$£-809]#,##0.00"/>
-    <numFmt numFmtId="170" formatCode="&quot; &quot;* #,##0&quot; &quot;;&quot;-&quot;* #,##0&quot; &quot;;&quot; &quot;* &quot;-&quot;??&quot; &quot;"/>
-    <numFmt numFmtId="171" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="172" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* &quot;-&quot;??\ _€_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="165" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="166" formatCode="dd/mm/yy;@"/>
+    <numFmt numFmtId="167" formatCode="[$£-809]#,##0.00;&quot;-&quot;[$£-809]#,##0.00"/>
+    <numFmt numFmtId="168" formatCode="&quot; &quot;* #,##0&quot; &quot;;&quot;-&quot;* #,##0&quot; &quot;;&quot; &quot;* &quot;-&quot;??&quot; &quot;"/>
+    <numFmt numFmtId="169" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="170" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* &quot;-&quot;??\ _€_-;_-@_-"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -229,7 +229,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -245,6 +245,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -369,10 +375,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
@@ -396,22 +402,28 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="4" fillId="0" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="172" fontId="4" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="170" fontId="4" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="170" fontId="6" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="6" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -419,40 +431,34 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="2" fillId="2" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="5" fillId="2" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="5" fillId="2" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -948,40 +954,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.5">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="14"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="16"/>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="16"/>
+      <c r="A2" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="18"/>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="1"/>
-      <c r="B3" s="17" t="str">
+      <c r="B3" s="22" t="str">
         <f>"From"</f>
         <v>From</v>
       </c>
-      <c r="C3" s="18" t="str">
+      <c r="C3" s="19" t="str">
         <f>$D$6</f>
         <v>2015-09-21</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="21" t="s">
         <v>2</v>
       </c>
       <c r="E3" s="20" t="str">
@@ -1014,28 +1020,28 @@
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="22" t="s">
+      <c r="C5" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="22" t="s">
+      <c r="D5" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="22" t="s">
+      <c r="E5" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="22" t="s">
+      <c r="F5" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="22" t="s">
+      <c r="G5" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="H5" s="22" t="s">
+      <c r="H5" s="14" t="s">
         <v>11</v>
       </c>
     </row>
